--- a/dashboard/Houston_Community_Resource_Dashboard.xlsx
+++ b/dashboard/Houston_Community_Resource_Dashboard.xlsx
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -710,7 +710,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -732,17 +732,25 @@
           <t>77023</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>713-929-2330</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>aama.org</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Free ESL adult basic education GED computer literacy and workforce certification classes plus free child care for qualifying students. Contact via 211texas.org.</t>
+          <t>Free ESL adult basic education GED computer literacy and workforce certification classes plus free child care for qualifying students.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -764,10 +772,14 @@
           <t>77009</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>713-869-1684</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>avance.org</t>
+          <t>avancehouston.org</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -778,7 +790,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -814,7 +826,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -832,7 +844,11 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>713-692-6216</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>hcde-texas.org</t>
@@ -846,7 +862,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -864,7 +880,11 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>832-393-1313</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>houstonlibrary.org</t>
@@ -878,7 +898,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -897,10 +917,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77043</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>77080</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>713-468-4516</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>mamhouston.org</t>
@@ -914,7 +938,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -928,15 +952,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Northwest Houston</t>
+          <t>East Houston</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77092</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>77029</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>713-223-3700</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>houstonfoodbank.org</t>
@@ -950,7 +978,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -964,12 +992,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Downtown</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77006</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -990,7 +1018,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -1008,7 +1036,11 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>713-695-5437</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>kidsmealsinc.org</t>
@@ -1022,7 +1054,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -1044,7 +1076,11 @@
           <t>77026</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>713-226-4953</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>targethunger.org</t>
@@ -1058,7 +1094,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -1080,8 +1116,16 @@
           <t>77011</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>713-660-1880</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>elcentrodecorazon.org</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Federally qualified health center serving low-income and predominantly Hispanic families in Houston's East End with medical and dental care.</t>
@@ -1090,7 +1134,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -1112,8 +1156,16 @@
           <t>77036</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>713-773-0803</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>hopechc.org</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Multicultural community health center providing primary medical dental and behavioral health care for low-income and immigrant families.</t>
@@ -1122,7 +1174,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1192,11 @@
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>832-548-5000</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>legacycommunityhealth.org</t>
@@ -1154,7 +1210,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -1173,10 +1229,14 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>77074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>713-273-3700</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>bakerripley.org</t>
@@ -1190,7 +1250,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1272,11 @@
           <t>77072</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>281-530-6888</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>bpsos.org</t>
@@ -1226,7 +1290,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -1240,15 +1304,19 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Spring Branch</t>
+          <t>Sharpstown</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77055</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
+          <t>77074</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>346-200-9951</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>cwshouston.org</t>
@@ -1262,7 +1330,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -1302,7 +1370,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1388,11 @@
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>979-255-5188</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>houstonwelcomesrefugees.com</t>
@@ -1338,7 +1410,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Refugee Services of Texas - Houston</t>
+          <t>USCRI Houston</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1353,24 +1425,28 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77036</t>
+          <t>77082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>refugees.org</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Resettlement support and case management for refugees asylees and survivors of trafficking from more than 30 countries of origin. Contact via 211texas.org for current details.</t>
+          <t>Field office of the U.S. Committee for Refugees and Immigrants providing integration support health navigation and partner referrals for newly arrived families.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>The Alliance for Multicultural Community Services</t>
+          <t>YMCA International Services</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1380,93 +1456,25 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Gulfton</t>
+          <t>Southwest Houston</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>77057</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>346-297-2373</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ymcahouston.org</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Three-decade-old agency helping refugees immigrants and low-income residents with cultural adjustment economic self-sufficiency and mental health support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>USCRI Houston</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Refugee &amp; Immigration Services</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Southwest Houston</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>77036</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>refugees.org</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Field office of the U.S. Committee for Refugees and Immigrants providing integration support health navigation and partner referrals for newly arrived families.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>YMCA International Services</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Refugee &amp; Immigration Services</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Gulfton</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>77081</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>346-297-2373</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>ymcahouston.org</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Case management cultural orientation employment services and immigration legal help for refugees and immigrants in one of Houston's most diverse zip codes.</t>
         </is>
@@ -1546,23 +1554,23 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A4,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A4,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A4,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A4,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A4,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -1577,23 +1585,23 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A5,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A5,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A5,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A5,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A5,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -1608,23 +1616,23 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A6,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A6,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A6,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A6,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A6,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -1639,23 +1647,23 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A7,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A7,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A7,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A7,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A7,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -1666,27 +1674,27 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>East End</t>
+          <t>Downtown</t>
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A8,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A8,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A8,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A8,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A8,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -1697,27 +1705,27 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>East End</t>
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A9,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A9,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A9,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A9,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A9,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -1728,27 +1736,27 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>East Houston</t>
         </is>
       </c>
       <c r="B10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A10,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A10,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A10,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A10,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A10,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1759,27 +1767,27 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Near Northside</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="B11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A11,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A11,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A11,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A11,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A11,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G11" s="6">
@@ -1790,27 +1798,27 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Northside</t>
+          <t>Near Northside</t>
         </is>
       </c>
       <c r="B12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A12,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A12,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A12,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A12,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A12,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G12" s="6">
@@ -1821,27 +1829,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Northwest Houston</t>
+          <t>Northside</t>
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A13,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A13,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A13,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A13,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A13,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G13" s="6">
@@ -1856,23 +1864,23 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A14,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A14,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A14,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A14,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A14,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G14" s="6">
@@ -1887,23 +1895,23 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A15,Resources!$C$2:$C$23,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,B$3)</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A15,Resources!$C$2:$C$23,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,C$3)</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A15,Resources!$C$2:$C$23,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,D$3)</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A15,Resources!$C$2:$C$23,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,E$3)</f>
         <v/>
       </c>
       <c r="F15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A15,Resources!$C$2:$C$23,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,F$3)</f>
         <v/>
       </c>
       <c r="G15" s="6">
@@ -1988,7 +1996,7 @@
         </is>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A5,Resources!$C$2:$C$23,$B5)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,$B5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -2008,7 +2016,7 @@
         </is>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A6,Resources!$C$2:$C$23,$B6)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,$B6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
@@ -2028,7 +2036,7 @@
         </is>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A7,Resources!$C$2:$C$23,$B7)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,$B7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
@@ -2048,7 +2056,7 @@
         </is>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A8,Resources!$C$2:$C$23,$B8)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,$B8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
@@ -2068,7 +2076,7 @@
         </is>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A9,Resources!$C$2:$C$23,$B9)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,$B9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
@@ -2088,7 +2096,7 @@
         </is>
       </c>
       <c r="C10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A10,Resources!$C$2:$C$23,$B10)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,$B10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
@@ -2108,7 +2116,7 @@
         </is>
       </c>
       <c r="C11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A11,Resources!$C$2:$C$23,$B11)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,$B11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
@@ -2128,7 +2136,7 @@
         </is>
       </c>
       <c r="C12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A12,Resources!$C$2:$C$23,$B12)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,$B12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
@@ -2148,7 +2156,7 @@
         </is>
       </c>
       <c r="C13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A13,Resources!$C$2:$C$23,$B13)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,$B13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
@@ -2168,7 +2176,7 @@
         </is>
       </c>
       <c r="C14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A14,Resources!$C$2:$C$23,$B14)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,$B14)</f>
         <v/>
       </c>
       <c r="D14" s="6">
@@ -2188,7 +2196,7 @@
         </is>
       </c>
       <c r="C15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A15,Resources!$C$2:$C$23,$B15)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,$B15)</f>
         <v/>
       </c>
       <c r="D15" s="6">
@@ -2208,7 +2216,7 @@
         </is>
       </c>
       <c r="C16" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A16,Resources!$C$2:$C$23,$B16)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A16,Resources!$C$2:$C$21,$B16)</f>
         <v/>
       </c>
       <c r="D16" s="6">
@@ -2228,7 +2236,7 @@
         </is>
       </c>
       <c r="C17" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A17,Resources!$C$2:$C$23,$B17)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A17,Resources!$C$2:$C$21,$B17)</f>
         <v/>
       </c>
       <c r="D17" s="6">
@@ -2248,7 +2256,7 @@
         </is>
       </c>
       <c r="C18" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A18,Resources!$C$2:$C$23,$B18)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A18,Resources!$C$2:$C$21,$B18)</f>
         <v/>
       </c>
       <c r="D18" s="6">
@@ -2268,7 +2276,7 @@
         </is>
       </c>
       <c r="C19" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A19,Resources!$C$2:$C$23,$B19)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A19,Resources!$C$2:$C$21,$B19)</f>
         <v/>
       </c>
       <c r="D19" s="6">
@@ -2288,7 +2296,7 @@
         </is>
       </c>
       <c r="C20" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A20,Resources!$C$2:$C$23,$B20)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A20,Resources!$C$2:$C$21,$B20)</f>
         <v/>
       </c>
       <c r="D20" s="6">
@@ -2308,7 +2316,7 @@
         </is>
       </c>
       <c r="C21" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A21,Resources!$C$2:$C$23,$B21)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A21,Resources!$C$2:$C$21,$B21)</f>
         <v/>
       </c>
       <c r="D21" s="6">
@@ -2328,7 +2336,7 @@
         </is>
       </c>
       <c r="C22" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A22,Resources!$C$2:$C$23,$B22)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A22,Resources!$C$2:$C$21,$B22)</f>
         <v/>
       </c>
       <c r="D22" s="6">
@@ -2348,7 +2356,7 @@
         </is>
       </c>
       <c r="C23" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A23,Resources!$C$2:$C$23,$B23)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A23,Resources!$C$2:$C$21,$B23)</f>
         <v/>
       </c>
       <c r="D23" s="6">
@@ -2368,7 +2376,7 @@
         </is>
       </c>
       <c r="C24" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$23,$A24,Resources!$C$2:$C$23,$B24)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$21,$A24,Resources!$C$2:$C$21,$B24)</f>
         <v/>
       </c>
       <c r="D24" s="6">

--- a/dashboard/Houston_Community_Resource_Dashboard.xlsx
+++ b/dashboard/Houston_Community_Resource_Dashboard.xlsx
@@ -262,12 +262,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$4:$A$15</f>
+              <f>'Summary'!$A$4:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$G$4:$G$15</f>
+              <f>'Summary'!$G$4:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -343,7 +343,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="3240000"/>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -710,712 +710,720 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AAMA Adelante Adult Literacy</t>
+          <t>Casa Juan Diego</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; ESL</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>East End</t>
+          <t>Houston Heights</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>77023</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>713-929-2330</t>
+          <t>713-869-7376</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>aama.org</t>
+          <t>cjd.org</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Free ESL adult basic education GED computer literacy and workforce certification classes plus free child care for qualifying students.</t>
+          <t>Catholic Worker house of hospitality offering weekly free food and clothing distribution plus household-goods assistance specifically for immigrant and refugee families.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AVANCE-Houston</t>
+          <t>Christian Community Service Center - Emergency Services Central</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; ESL</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Northside</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>77027</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>713-869-1684</t>
+          <t>713-871-9741</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>avancehouston.org</t>
+          <t>ccschouston.org</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Parent and early-childhood education programs including ESL Head Start and General Equivalency Diploma preparation for low-income families.</t>
+          <t>This Emergency Services Central location provides gently used clothing diapers hygiene kits and a five-day food package after a walk-in interview; CCSC's Southwest branch offers food and hygiene only not clothing.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BakerRipley Adult Education</t>
+          <t>Emergency Aid Coalition - Clothing Center</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; ESL</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Citywide</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Third Ward</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77004</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>713-273-3719</t>
+          <t>713-343-3061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>economicinitiatives.bakerripley.org</t>
+          <t>eachouston.org</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Free ESL GED and computer literacy classes for adult learners at multiple campuses across Harris County with no minimum education requirement.</t>
+          <t>Free clothing up to two outfits per person shoes when available toiletries and underwear for men women and children with visits by appointment only.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HCDE Adult Education ESL</t>
+          <t>Faith Center Spring Branch</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; ESL</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Citywide</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>Spring Branch</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77055</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>713-692-6216</t>
+          <t>713-554-8820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>hcde-texas.org</t>
+          <t>houstonsfirst.org</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Harris County Department of Education program offering free beginning through advanced ESL classes online and in person across the county.</t>
+          <t>Free food pantry and clothes closet providing groceries clothing and hygiene essentials to Spring Branch families with visits by appointment.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Houston Public Library - Cultural Connections &amp; ESL</t>
+          <t>Houston Furniture Bank</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; ESL</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Citywide</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>South Houston</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77075</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>832-393-1313</t>
+          <t>713-842-9777</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>houstonlibrary.org</t>
+          <t>houstonfurniturebank.org</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Free English and language-learning classes plus cultural-orientation programming open to new immigrants at branches across the city.</t>
+          <t>Provides free furniture such as beds tables seating and mattresses to families in need but only through referral from a partner social-service agency not direct walk-in.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Literacy Advance - Memorial Assistance Ministries</t>
+          <t>Lilly Grove Missionary Baptist Church - Clothes Closet</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Education &amp; ESL</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Spring Branch</t>
+          <t>South Union</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77080</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>713-468-4516</t>
+          <t>713-748-7324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>mamhouston.org</t>
+          <t>lillygrove.org</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Free English and reading classes for adults running since 1964 supported by volunteer tutors plus citizenship and employment-readiness classes.</t>
+          <t>Free clothing for men women and children including suits shirts casual wear shoes undergarments uniforms and backpacks from a dedicated house across from the church.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Houston Food Bank</t>
+          <t>Memorial Assistance Ministries - Resale &amp; Voucher Program</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Food Assistance</t>
+          <t>Clothing &amp; Household Goods</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>East Houston</t>
+          <t>Spring Branch</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77029</t>
+          <t>77080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>713-223-3700</t>
+          <t>713-491-4330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>houstonfoodbank.org</t>
+          <t>mamhouston.org</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Largest hunger-relief organization in southeast Texas coordinating pantries meal programs and produce distributions across 18 counties.</t>
+          <t>Issues clothing and furniture vouchers redeemable at the MAM Resale Store which also sells low-cost clothing home furnishings electronics and household items.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Interfaith Ministries for Greater Houston</t>
+          <t>AAMA Adelante Adult Literacy</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Food Assistance</t>
+          <t>Education &amp; ESL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Downtown</t>
+          <t>East End</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>77023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>713-533-4900</t>
+          <t>713-929-2330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>imgh.org</t>
+          <t>aama.org</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Emergency food assistance and a Meals on Wheels senior meals program alongside refugee housing English classes and job placement support.</t>
+          <t>Free ESL adult basic education GED computer literacy and workforce certification classes plus free child care for qualifying students.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kids' Meals</t>
+          <t>AVANCE-Houston</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Food Assistance</t>
+          <t>Education &amp; ESL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Citywide</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>Northside</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77009</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>713-695-5437</t>
+          <t>713-869-1684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>kidsmealsinc.org</t>
+          <t>avancehouston.org</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Delivers free healthy meals on weekdays to the homes of children under six and connects families to a broader support network.</t>
+          <t>Parent and early-childhood education programs including ESL Head Start and General Equivalency Diploma preparation for low-income families.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Target Hunger</t>
+          <t>BakerRipley Adult Education</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Food Assistance</t>
+          <t>Education &amp; ESL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Near Northside</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77026</t>
-        </is>
-      </c>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>713-226-4953</t>
+          <t>713-273-3719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>targethunger.org</t>
+          <t>economicinitiatives.bakerripley.org</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Food assistance and navigation programs that provided food to more than 25000 individuals and 9200 households across Houston in 2025.</t>
+          <t>Free ESL GED and computer literacy classes for adult learners at multiple campuses across Harris County with no minimum education requirement.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>El Centro de Corazon</t>
+          <t>HCDE Adult Education ESL</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Education &amp; ESL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>East End</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77011</t>
-        </is>
-      </c>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>713-660-1880</t>
+          <t>713-692-6216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>elcentrodecorazon.org</t>
+          <t>hcde-texas.org</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Federally qualified health center serving low-income and predominantly Hispanic families in Houston's East End with medical and dental care.</t>
+          <t>Harris County Department of Education program offering free beginning through advanced ESL classes online and in person across the county.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>HOPE Clinic</t>
+          <t>Houston Public Library - Cultural Connections &amp; ESL</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Education &amp; ESL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Southwest Houston</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>77036</t>
-        </is>
-      </c>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>713-773-0803</t>
+          <t>832-393-1313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>hopechc.org</t>
+          <t>houstonlibrary.org</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Multicultural community health center providing primary medical dental and behavioral health care for low-income and immigrant families.</t>
+          <t>Free English and language-learning classes plus cultural-orientation programming open to new immigrants at branches across the city.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Legacy Community Health</t>
+          <t>Literacy Advance - Memorial Assistance Ministries</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Education &amp; ESL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Citywide</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>Spring Branch</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77080</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>832-548-5000</t>
+          <t>713-468-4516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>legacycommunityhealth.org</t>
+          <t>mamhouston.org</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Federally qualified health network with clinics across Houston offering sliding-scale primary care for low-income and uninsured residents.</t>
+          <t>Free English and reading classes for adults running since 1964 supported by volunteer tutors plus citizenship and employment-readiness classes.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BakerRipley Gulfton-Sharpstown Campus</t>
+          <t>Houston Food Bank</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Multi-Service Community Center</t>
+          <t>Food Assistance</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Gulfton</t>
+          <t>East Houston</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77074</t>
+          <t>77029</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>713-273-3700</t>
+          <t>713-223-3700</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>bakerripley.org</t>
+          <t>houstonfoodbank.org</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Five-building neighborhood campus offering early childhood education youth programs immigration services and a community garden for residents from 80-plus countries.</t>
+          <t>Largest hunger-relief organization in southeast Texas coordinating pantries meal programs and produce distributions across 18 counties.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BPSOS-Houston</t>
+          <t>Interfaith Ministries for Greater Houston</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Refugee &amp; Immigration Services</t>
+          <t>Food Assistance</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Alief</t>
+          <t>Downtown</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77072</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>281-530-6888</t>
+          <t>713-533-4900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>bpsos.org</t>
+          <t>imgh.org</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Boat People S.O.S. affiliate supporting Vietnamese and other Southeast Asian immigrant and refugee families with case management and civic engagement.</t>
+          <t>Emergency food assistance and a Meals on Wheels senior meals program alongside refugee housing English classes and job placement support.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CWS Houston</t>
+          <t>Kids' Meals</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Refugee &amp; Immigration Services</t>
+          <t>Food Assistance</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sharpstown</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>77074</t>
-        </is>
-      </c>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346-200-9951</t>
+          <t>713-695-5437</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>cwshouston.org</t>
+          <t>kidsmealsinc.org</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Resettlement case management housing assistance ESL and cultural orientation referrals and support for unaccompanied minors transitioning into local care.</t>
+          <t>Delivers free healthy meals on weekdays to the homes of children under six and connects families to a broader support network.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Catholic Charities of the Archdiocese of Galveston-Houston</t>
+          <t>Target Hunger</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Refugee &amp; Immigration Services</t>
+          <t>Food Assistance</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Near Northside</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77006</t>
+          <t>77026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>713-526-4611</t>
+          <t>713-226-4953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>catholiccharities.org</t>
+          <t>targethunger.org</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Refugee resettlement immigration legal services family strengthening and senior services serving more than 85000 people a year across the region.</t>
+          <t>Food assistance and navigation programs that provided food to more than 25000 individuals and 9200 households across Houston in 2025.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Houston Welcomes Refugees</t>
+          <t>El Centro de Corazon</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Refugee &amp; Immigration Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Citywide</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>East End</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>77011</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>979-255-5188</t>
+          <t>713-660-1880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>houstonwelcomesrefugees.com</t>
+          <t>elcentrodecorazon.org</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Volunteer welcome teams that deliver welcome kits and groceries and connect newly arrived refugees to critical resources in their first months.</t>
+          <t>Federally qualified health center serving low-income and predominantly Hispanic families in Houston's East End with medical and dental care.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>USCRI Houston</t>
+          <t>HOPE Clinic</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Refugee &amp; Immigration Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1425,56 +1433,328 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>77036</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>713-773-0803</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>refugees.org</t>
+          <t>hopechc.org</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Field office of the U.S. Committee for Refugees and Immigrants providing integration support health navigation and partner referrals for newly arrived families.</t>
+          <t>Multicultural community health center providing primary medical dental and behavioral health care for low-income and immigrant families.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Community Health</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>832-548-5000</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>legacycommunityhealth.org</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Federally qualified health network with clinics across Houston offering sliding-scale primary care for low-income and uninsured residents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>BakerRipley Gulfton-Sharpstown Campus</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Multi-Service Community Center</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Gulfton</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>77074</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>713-273-3700</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>bakerripley.org</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Five-building neighborhood campus offering early childhood education youth programs immigration services and a community garden for residents from 80-plus countries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BPSOS-Houston</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Refugee &amp; Immigration Services</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Alief</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>77072</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>281-530-6888</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>bpsos.org</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Boat People S.O.S. affiliate supporting Vietnamese and other Southeast Asian immigrant and refugee families with case management and civic engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CWS Houston</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Refugee &amp; Immigration Services</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sharpstown</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>77074</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>346-200-9951</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>cwshouston.org</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Resettlement case management housing assistance ESL and cultural orientation referrals and support for unaccompanied minors transitioning into local care.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Catholic Charities of the Archdiocese of Galveston-Houston</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Refugee &amp; Immigration Services</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Midtown</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>77006</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>713-526-4611</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>catholiccharities.org</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Refugee resettlement immigration legal services family strengthening and senior services serving more than 85000 people a year across the region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Houston Welcomes Refugees</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Refugee &amp; Immigration Services</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>979-255-5188</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>houstonwelcomesrefugees.com</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Volunteer welcome teams that deliver welcome kits and groceries and connect newly arrived refugees to critical resources in their first months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>USCRI Houston</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Refugee &amp; Immigration Services</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Southwest Houston</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>77082</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>refugees.org</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Field office of the U.S. Committee for Refugees and Immigrants providing integration support health navigation and partner referrals for newly arrived families.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>YMCA International Services</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Refugee &amp; Immigration Services</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Southwest Houston</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>77057</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>346-297-2373</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>ymcahouston.org</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case management cultural orientation employment services and immigration legal help for refugees and immigrants in one of Houston's most diverse zip codes.</t>
         </is>
@@ -1491,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1554,23 +1834,23 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A4,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A4,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A4,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A4,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A4,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A4,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -1585,23 +1865,23 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A5,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A5,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A5,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A5,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A5,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -1616,23 +1896,23 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A6,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A6,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A6,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A6,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A6,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -1647,23 +1927,23 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A7,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A7,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A7,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A7,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A7,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -1678,23 +1958,23 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A8,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A8,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A8,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A8,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A8,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -1709,23 +1989,23 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A9,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A9,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A9,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A9,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A9,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -1740,23 +2020,23 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A10,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A10,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A10,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A10,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A10,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1767,27 +2047,27 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="B11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A11,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A11,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A11,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A11,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A11,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G11" s="6">
@@ -1798,27 +2078,27 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Near Northside</t>
+          <t>Houston Heights</t>
         </is>
       </c>
       <c r="B12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A12,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A12,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A12,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A12,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A12,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G12" s="6">
@@ -1829,27 +2109,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Northside</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A13,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A13,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A13,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A13,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A13,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G13" s="6">
@@ -1860,27 +2140,27 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Southwest Houston</t>
+          <t>Near Northside</t>
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A14,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A14,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A14,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A14,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A14,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G14" s="6">
@@ -1891,31 +2171,186 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Citywide</t>
+          <t>Northside</t>
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,B$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A15,Resources!$C$2:$C$28,B$3)</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,C$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A15,Resources!$C$2:$C$28,C$3)</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,D$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A15,Resources!$C$2:$C$28,D$3)</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,E$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A15,Resources!$C$2:$C$28,E$3)</f>
         <v/>
       </c>
       <c r="F15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,F$3)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A15,Resources!$C$2:$C$28,F$3)</f>
         <v/>
       </c>
       <c r="G15" s="6">
         <f>SUM(B15:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>South Houston</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A16,Resources!$C$2:$C$28,B$3)</f>
+        <v/>
+      </c>
+      <c r="C16" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A16,Resources!$C$2:$C$28,C$3)</f>
+        <v/>
+      </c>
+      <c r="D16" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A16,Resources!$C$2:$C$28,D$3)</f>
+        <v/>
+      </c>
+      <c r="E16" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A16,Resources!$C$2:$C$28,E$3)</f>
+        <v/>
+      </c>
+      <c r="F16" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A16,Resources!$C$2:$C$28,F$3)</f>
+        <v/>
+      </c>
+      <c r="G16" s="6">
+        <f>SUM(B16:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>South Union</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A17,Resources!$C$2:$C$28,B$3)</f>
+        <v/>
+      </c>
+      <c r="C17" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A17,Resources!$C$2:$C$28,C$3)</f>
+        <v/>
+      </c>
+      <c r="D17" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A17,Resources!$C$2:$C$28,D$3)</f>
+        <v/>
+      </c>
+      <c r="E17" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A17,Resources!$C$2:$C$28,E$3)</f>
+        <v/>
+      </c>
+      <c r="F17" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A17,Resources!$C$2:$C$28,F$3)</f>
+        <v/>
+      </c>
+      <c r="G17" s="6">
+        <f>SUM(B17:F17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Southwest Houston</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A18,Resources!$C$2:$C$28,B$3)</f>
+        <v/>
+      </c>
+      <c r="C18" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A18,Resources!$C$2:$C$28,C$3)</f>
+        <v/>
+      </c>
+      <c r="D18" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A18,Resources!$C$2:$C$28,D$3)</f>
+        <v/>
+      </c>
+      <c r="E18" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A18,Resources!$C$2:$C$28,E$3)</f>
+        <v/>
+      </c>
+      <c r="F18" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A18,Resources!$C$2:$C$28,F$3)</f>
+        <v/>
+      </c>
+      <c r="G18" s="6">
+        <f>SUM(B18:F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Third Ward</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A19,Resources!$C$2:$C$28,B$3)</f>
+        <v/>
+      </c>
+      <c r="C19" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A19,Resources!$C$2:$C$28,C$3)</f>
+        <v/>
+      </c>
+      <c r="D19" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A19,Resources!$C$2:$C$28,D$3)</f>
+        <v/>
+      </c>
+      <c r="E19" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A19,Resources!$C$2:$C$28,E$3)</f>
+        <v/>
+      </c>
+      <c r="F19" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A19,Resources!$C$2:$C$28,F$3)</f>
+        <v/>
+      </c>
+      <c r="G19" s="6">
+        <f>SUM(B19:F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Citywide</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A20,Resources!$C$2:$C$28,B$3)</f>
+        <v/>
+      </c>
+      <c r="C20" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A20,Resources!$C$2:$C$28,C$3)</f>
+        <v/>
+      </c>
+      <c r="D20" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A20,Resources!$C$2:$C$28,D$3)</f>
+        <v/>
+      </c>
+      <c r="E20" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A20,Resources!$C$2:$C$28,E$3)</f>
+        <v/>
+      </c>
+      <c r="F20" s="6">
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A20,Resources!$C$2:$C$28,F$3)</f>
+        <v/>
+      </c>
+      <c r="G20" s="6">
+        <f>SUM(B20:F20)</f>
         <v/>
       </c>
     </row>
@@ -1923,7 +2358,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:F15">
+  <conditionalFormatting sqref="B4:F20">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1996,7 +2431,7 @@
         </is>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A5,Resources!$C$2:$C$21,$B5)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A5,Resources!$C$2:$C$28,$B5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -2016,7 +2451,7 @@
         </is>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A6,Resources!$C$2:$C$21,$B6)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A6,Resources!$C$2:$C$28,$B6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
@@ -2036,7 +2471,7 @@
         </is>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A7,Resources!$C$2:$C$21,$B7)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A7,Resources!$C$2:$C$28,$B7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
@@ -2056,7 +2491,7 @@
         </is>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A8,Resources!$C$2:$C$21,$B8)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A8,Resources!$C$2:$C$28,$B8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
@@ -2076,7 +2511,7 @@
         </is>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A9,Resources!$C$2:$C$21,$B9)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A9,Resources!$C$2:$C$28,$B9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
@@ -2096,7 +2531,7 @@
         </is>
       </c>
       <c r="C10" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A10,Resources!$C$2:$C$21,$B10)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A10,Resources!$C$2:$C$28,$B10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
@@ -2116,7 +2551,7 @@
         </is>
       </c>
       <c r="C11" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A11,Resources!$C$2:$C$21,$B11)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A11,Resources!$C$2:$C$28,$B11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
@@ -2136,7 +2571,7 @@
         </is>
       </c>
       <c r="C12" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A12,Resources!$C$2:$C$21,$B12)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A12,Resources!$C$2:$C$28,$B12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
@@ -2156,7 +2591,7 @@
         </is>
       </c>
       <c r="C13" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A13,Resources!$C$2:$C$21,$B13)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A13,Resources!$C$2:$C$28,$B13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
@@ -2176,7 +2611,7 @@
         </is>
       </c>
       <c r="C14" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A14,Resources!$C$2:$C$21,$B14)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A14,Resources!$C$2:$C$28,$B14)</f>
         <v/>
       </c>
       <c r="D14" s="6">
@@ -2196,7 +2631,7 @@
         </is>
       </c>
       <c r="C15" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A15,Resources!$C$2:$C$21,$B15)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A15,Resources!$C$2:$C$28,$B15)</f>
         <v/>
       </c>
       <c r="D15" s="6">
@@ -2216,7 +2651,7 @@
         </is>
       </c>
       <c r="C16" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A16,Resources!$C$2:$C$21,$B16)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A16,Resources!$C$2:$C$28,$B16)</f>
         <v/>
       </c>
       <c r="D16" s="6">
@@ -2236,7 +2671,7 @@
         </is>
       </c>
       <c r="C17" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A17,Resources!$C$2:$C$21,$B17)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A17,Resources!$C$2:$C$28,$B17)</f>
         <v/>
       </c>
       <c r="D17" s="6">
@@ -2256,7 +2691,7 @@
         </is>
       </c>
       <c r="C18" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A18,Resources!$C$2:$C$21,$B18)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A18,Resources!$C$2:$C$28,$B18)</f>
         <v/>
       </c>
       <c r="D18" s="6">
@@ -2276,7 +2711,7 @@
         </is>
       </c>
       <c r="C19" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A19,Resources!$C$2:$C$21,$B19)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A19,Resources!$C$2:$C$28,$B19)</f>
         <v/>
       </c>
       <c r="D19" s="6">
@@ -2296,7 +2731,7 @@
         </is>
       </c>
       <c r="C20" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A20,Resources!$C$2:$C$21,$B20)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A20,Resources!$C$2:$C$28,$B20)</f>
         <v/>
       </c>
       <c r="D20" s="6">
@@ -2316,7 +2751,7 @@
         </is>
       </c>
       <c r="C21" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A21,Resources!$C$2:$C$21,$B21)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A21,Resources!$C$2:$C$28,$B21)</f>
         <v/>
       </c>
       <c r="D21" s="6">
@@ -2336,7 +2771,7 @@
         </is>
       </c>
       <c r="C22" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A22,Resources!$C$2:$C$21,$B22)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A22,Resources!$C$2:$C$28,$B22)</f>
         <v/>
       </c>
       <c r="D22" s="6">
@@ -2356,7 +2791,7 @@
         </is>
       </c>
       <c r="C23" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A23,Resources!$C$2:$C$21,$B23)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A23,Resources!$C$2:$C$28,$B23)</f>
         <v/>
       </c>
       <c r="D23" s="6">
@@ -2376,7 +2811,7 @@
         </is>
       </c>
       <c r="C24" s="6">
-        <f>COUNTIFS(Resources!$D$2:$D$21,$A24,Resources!$C$2:$C$21,$B24)</f>
+        <f>COUNTIFS(Resources!$D$2:$D$28,$A24,Resources!$C$2:$C$28,$B24)</f>
         <v/>
       </c>
       <c r="D24" s="6">
